--- a/Project_ETF/ETF_Investment_Portfolio/00403A/ETF_Investment_Portfolio_20260616.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/00403A/ETF_Investment_Portfolio_20260616.xlsx
@@ -1305,17 +1305,17 @@
     <row r="53">
       <c r="A53" s="3" t="inlineStr">
         <is>
-          <t>6805</t>
+          <t>8046</t>
         </is>
       </c>
       <c r="B53" s="3" t="inlineStr">
         <is>
-          <t>富世達</t>
+          <t>南電</t>
         </is>
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>570,000</t>
+          <t>1,080,000</t>
         </is>
       </c>
       <c r="D53" s="4" t="inlineStr">
@@ -1327,17 +1327,17 @@
     <row r="54">
       <c r="A54" s="3" t="inlineStr">
         <is>
-          <t>8046</t>
+          <t>6805</t>
         </is>
       </c>
       <c r="B54" s="3" t="inlineStr">
         <is>
-          <t>南電</t>
+          <t>富世達</t>
         </is>
       </c>
       <c r="C54" s="4" t="inlineStr">
         <is>
-          <t>1,080,000</t>
+          <t>570,000</t>
         </is>
       </c>
       <c r="D54" s="4" t="inlineStr">
@@ -1437,17 +1437,17 @@
     <row r="59">
       <c r="A59" s="3" t="inlineStr">
         <is>
-          <t>3583</t>
+          <t>8210</t>
         </is>
       </c>
       <c r="B59" s="3" t="inlineStr">
         <is>
-          <t>辛耘</t>
+          <t>勤誠</t>
         </is>
       </c>
       <c r="C59" s="4" t="inlineStr">
         <is>
-          <t>900,000</t>
+          <t>540,000</t>
         </is>
       </c>
       <c r="D59" s="4" t="inlineStr">
@@ -1459,17 +1459,17 @@
     <row r="60">
       <c r="A60" s="3" t="inlineStr">
         <is>
-          <t>8210</t>
+          <t>3583</t>
         </is>
       </c>
       <c r="B60" s="3" t="inlineStr">
         <is>
-          <t>勤誠</t>
+          <t>辛耘</t>
         </is>
       </c>
       <c r="C60" s="4" t="inlineStr">
         <is>
-          <t>540,000</t>
+          <t>900,000</t>
         </is>
       </c>
       <c r="D60" s="4" t="inlineStr">
